--- a/data/Data.xlsx
+++ b/data/Data.xlsx
@@ -165,7 +165,7 @@
   <commentList>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Team Leaders only. List the consultants in this Team Leader's team, exactly as their names appear in the Enquiry sheet (Consultant Name), separated by semicolons. Example: Name One; Name Two; Name Three. A Team Leader sees ONLY these consultants' data (plus their own name). Leave blank for Full users.</t>
+        <t>Team Leaders only. List the consultants in this Team Leader's team, exactly as their names appear in the Enquiry sheet (Consultant Name), separated by semicolons. Example: Name One; Name Two; Name Three. Once filled, the Team Leader sees ONLY these consultants' data (plus their own name). LEAVE BLANK = the Team Leader sees all consultants, as before. Not used for Full users.</t>
       </text>
     </comment>
   </commentList>
